--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,6 +1363,33 @@
         </is>
       </c>
       <c r="E43" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DXj4ZZ_jcuR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:22:55 UTC</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXj4ZZ_jcuR/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="State" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1390,6 +1390,33 @@
         </is>
       </c>
       <c r="E44" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DYH6l0oNBOI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:25:01 UTC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYH6l0oNBOI/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,6 +1417,33 @@
         </is>
       </c>
       <c r="E45" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DV3tVLsjfsG</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-05-12 23:32:53 UTC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DV3tVLsjfsG/</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,6 +1444,33 @@
         </is>
       </c>
       <c r="E46" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DXCZTaUDUiH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:28:24 UTC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXCZTaUDUiH/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,6 +1471,33 @@
         </is>
       </c>
       <c r="E47" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DXR16EYDRgv</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-05-13 23:34:34 UTC</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXR16EYDRgv/</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,6 +1498,33 @@
         </is>
       </c>
       <c r="E48" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DWRbz3vjUYF</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-05-14 12:10:37 UTC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWRbz3vjUYF/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1525,6 +1525,33 @@
         </is>
       </c>
       <c r="E49" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DWtytopDdfd</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:15:41 UTC</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWtytopDdfd/</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1552,6 +1552,33 @@
         </is>
       </c>
       <c r="E50" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DWbw9uQDexu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:16:08 UTC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWbw9uQDexu/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1581,6 +1581,33 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DYPo83cNp0A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-05-15 23:16:26 UTC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYPo83cNp0A/</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,6 +1608,33 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DT8H1XNjaOx</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-05-16 11:29:55 UTC</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DT8H1XNjaOx/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>scenic</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,33 @@
         </is>
       </c>
       <c r="E53" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DVBqsc9jf6s</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-05-16 23:12:46 UTC</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVBqsc9jf6s/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1660,6 +1660,33 @@
         </is>
       </c>
       <c r="E54" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DTDeeVajUMy</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-05-17 11:35:47 UTC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DTDeeVajUMy/</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,6 +1687,33 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DVTqTxWDXov</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-05-17 23:15:22 UTC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVTqTxWDXov/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1714,6 +1714,33 @@
         </is>
       </c>
       <c r="E56" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DUOJeTTDZuO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-05-18 14:03:45 UTC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DUOJeTTDZuO/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,33 @@
         </is>
       </c>
       <c r="E57" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DTnh-OcDe52</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-05-18 23:33:41 UTC</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DTnh-OcDe52/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +1768,33 @@
         </is>
       </c>
       <c r="E58" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DSxdTJXjRdV</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:37:54 UTC</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DSxdTJXjRdV/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,6 +1795,33 @@
         </is>
       </c>
       <c r="E59" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DTVgTZPDedB</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-05-19 23:36:44 UTC</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DTVgTZPDedB/</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,6 +1824,33 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DU03Zk4jcyT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:41:34 UTC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DU03Zk4jcyT/</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1851,6 +1851,33 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DVlse0Ljc03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-05-20 23:42:59 UTC</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVlse0Ljc03/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>adventure</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1878,6 +1878,33 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>adventure</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CuKULRkK38O</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-05-21 23:32:35 UTC</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CuKULRkK38O/</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1905,6 +1905,33 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DRFTfHvjaw1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:37:43 UTC</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DRFTfHvjaw1/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>scenic</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1930,6 +1930,33 @@
         </is>
       </c>
       <c r="E64" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DPZJ3awDWzW</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-05-22 23:37:10 UTC</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DPZJ3awDWzW/</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1957,6 +1957,33 @@
         </is>
       </c>
       <c r="E65" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DSNZxVVjXwB</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-05-23 11:39:02 UTC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DSNZxVVjXwB/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,33 @@
         </is>
       </c>
       <c r="E66" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DR7X_XnjRqG</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-05-23 23:14:46 UTC</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DR7X_XnjRqG/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,6 +2011,33 @@
         </is>
       </c>
       <c r="E67" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DRXVCiGjTPY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-05-24 11:45:33 UTC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DRXVCiGjTPY/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2040,6 +2040,33 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DSDHsqRje56</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-05-24 23:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DSDHsqRje56/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>adventure</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2065,6 +2065,33 @@
         </is>
       </c>
       <c r="E69" t="inlineStr">
+        <is>
+          <t>adventure</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DQPOeN7DXwY</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-05-25 13:44:57 UTC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQPOeN7DXwY/</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>adventure</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2094,6 +2094,33 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>adventure</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DRpWud-DVei</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:35:46 UTC</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DRpWud-DVei/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>scenic</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2121,6 +2121,33 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DQhQXZ-jbW_</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:26:27 UTC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQhQXZ-jbW_/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>adventure</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,6 +2148,33 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>adventure</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DORDygWjauy</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-05-26 23:36:10 UTC</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DORDygWjauy/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>scenic</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2173,6 +2173,33 @@
         </is>
       </c>
       <c r="E73" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DNa_CYrKMhs</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:54:10 UTC</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DNa_CYrKMhs/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2200,6 +2200,33 @@
         </is>
       </c>
       <c r="E74" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DM0W4lqKaTu</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-05-27 23:40:58 UTC</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DM0W4lqKaTu/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,6 +2227,33 @@
         </is>
       </c>
       <c r="E75" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DN_B5N2Daqt</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:08:56 UTC</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DN_B5N2Daqt/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2254,6 +2254,33 @@
         </is>
       </c>
       <c r="E76" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DOjFNS9DbGO</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-05-28 23:46:05 UTC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DOjFNS9DbGO/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2281,6 +2281,33 @@
         </is>
       </c>
       <c r="E77" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DMA3BL6qkoR</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:39:36 UTC</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DMA3BL6qkoR/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,6 +2308,33 @@
         </is>
       </c>
       <c r="E78" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DO1G4NujWgc</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-05-29 23:46:27 UTC</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DO1G4NujWgc/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2335,6 +2335,33 @@
         </is>
       </c>
       <c r="E79" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DNI9YCoqh0e</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-05-30 11:48:44 UTC</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DNI9YCoqh0e/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2362,6 +2362,33 @@
         </is>
       </c>
       <c r="E80" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DNtAn-9Wjpa</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-05-30 23:30:47 UTC</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DNtAn-9Wjpa/</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2389,6 +2389,33 @@
         </is>
       </c>
       <c r="E81" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DLcz3GVq-KL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-05-31 11:53:24 UTC</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DLcz3GVq-KL/</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,6 +2416,33 @@
         </is>
       </c>
       <c r="E82" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DMS4u4mKnsE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-05-31 23:34:17 UTC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DMS4u4mKnsE/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2443,6 +2443,33 @@
         </is>
       </c>
       <c r="E83" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DPHIdPkDST-</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-06-01 23:46:25 UTC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DPHIdPkDST-/</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,6 +2470,33 @@
         </is>
       </c>
       <c r="E84" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DQW9TBnjUfL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-06-02 14:34:53 UTC</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQW9TBnjUfL/</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2497,6 +2497,33 @@
         </is>
       </c>
       <c r="E85" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DRNADedjVGz</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:07:45 UTC</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DRNADedjVGz/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,6 +2524,33 @@
         </is>
       </c>
       <c r="E86" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DQzR1vijVbM</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-06-03 15:08:43 UTC</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQzR1vijVbM/</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2553,6 +2553,33 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DKpUazjKAZB</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:08:31 UTC</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DKpUazjKAZB/</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>cultural</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2580,6 +2580,33 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>cultural</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DHydMZ2qB_C</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:34:20 UTC</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DHydMZ2qB_C/</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>scenic</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2607,6 +2607,33 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DIRWwJOKN2D</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:41:19 UTC</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DIRWwJOKN2D/</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2634,6 +2634,33 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DLKysmmqma4</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-06-05 13:30:10 UTC</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DLKysmmqma4/</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>scenic</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,33 @@
         </is>
       </c>
       <c r="E91" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DIEg-Oaq38s</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-06-05 23:41:46 UTC</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DIEg-Oaq38s/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2686,6 +2686,33 @@
         </is>
       </c>
       <c r="E92" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DK7VfueKrFA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-06-06 11:49:13 UTC</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DK7VfueKrFA/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2713,6 +2713,33 @@
         </is>
       </c>
       <c r="E93" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DJMvPSRquhl</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06-06 23:32:29 UTC</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DJMvPSRquhl/</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,6 +2740,33 @@
         </is>
       </c>
       <c r="E94" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DJwqhvnquRw</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-06-07 12:04:07 UTC</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DJwqhvnquRw/</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2767,6 +2767,33 @@
         </is>
       </c>
       <c r="E95" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DIokVo-o1Yp</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-06-07 23:32:54 UTC</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DIokVo-o1Yp/</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2794,6 +2794,33 @@
         </is>
       </c>
       <c r="E96" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DIWjBYhq9sN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-06-08 14:33:20 UTC</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DIWjBYhq9sN/</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2821,6 +2821,33 @@
         </is>
       </c>
       <c r="E97" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DSfbbtZjc04</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-06-08 23:41:41 UTC</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DSfbbtZjc04/</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2848,6 +2848,33 @@
         </is>
       </c>
       <c r="E98" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DI6lHXEqUDO</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06-09 13:19:38 UTC</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DI6lHXEqUDO/</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2875,6 +2875,33 @@
         </is>
       </c>
       <c r="E99" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DEIMZ_oqv_t</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:22 UTC</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DEIMZ_oqv_t/</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2902,6 +2902,33 @@
         </is>
       </c>
       <c r="E100" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DD2KCWeqltp</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06-10 23:52:52 UTC</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DD2KCWeqltp/</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2929,6 +2929,33 @@
         </is>
       </c>
       <c r="E101" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DDkIFnmKSXf</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-06-11 23:57:12 UTC</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DDkIFnmKSXf/</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,6 +2956,33 @@
         </is>
       </c>
       <c r="E102" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DDAFJT4q12u</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-06-12 23:57:09 UTC</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DDAFJT4q12u/</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2983,6 +2983,33 @@
         </is>
       </c>
       <c r="E103" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DGqYqyOqyPk</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-06-13 12:05:52 UTC</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DGqYqyOqyPk/</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3010,6 +3010,33 @@
         </is>
       </c>
       <c r="E104" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DFiTTjHqwXq</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-06-13 23:36:16 UTC</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DFiTTjHqwXq/</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,6 +3037,33 @@
         </is>
       </c>
       <c r="E105" t="inlineStr">
+        <is>
+          <t>scenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DE-P-yCqhM3</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-06-14 12:19:04 UTC</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DE-P-yCqhM3/</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>scenic</t>
         </is>
